--- a/deliverables/uiss/X15_UISS_Screen_MenuSettings.xlsx
+++ b/deliverables/uiss/X15_UISS_Screen_MenuSettings.xlsx
@@ -5289,7 +5289,7 @@
       <row>8</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5972175" cy="5086350"/>
+    <ext cx="5781675" cy="5086350"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -38825,7 +38825,7 @@
       </c>
       <c r="F17" s="1265" t="inlineStr">
         <is>
-          <t>Prototype: the setting is kept in the browser. In NSP it is saved in TB_M_MENU_VISIBILITY</t>
+          <t>Prototype: the setting is kept in the browser. In Supplier System it is saved in</t>
         </is>
       </c>
       <c r="G17" s="1136" t="n"/>
@@ -38934,7 +38934,7 @@
       <c r="E18" s="1136" t="n"/>
       <c r="F18" s="1145" t="inlineStr">
         <is>
-          <t>(proposed); per role or global is TBD.</t>
+          <t>TB_M_MENU_VISIBILITY (proposed); per role or global is TBD.</t>
         </is>
       </c>
       <c r="G18" s="1136" t="n"/>

--- a/deliverables/uiss/X15_UISS_Screen_MenuSettings.xlsx
+++ b/deliverables/uiss/X15_UISS_Screen_MenuSettings.xlsx
@@ -5289,7 +5289,7 @@
       <row>8</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5781675" cy="5086350"/>
+    <ext cx="5972175" cy="5086350"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -38825,7 +38825,7 @@
       </c>
       <c r="F17" s="1265" t="inlineStr">
         <is>
-          <t>Prototype: the setting is kept in the browser. In Supplier System it is saved in</t>
+          <t>Prototype: the setting is kept in the browser. In NSP it is saved in TB_M_MENU_VISIBILITY</t>
         </is>
       </c>
       <c r="G17" s="1136" t="n"/>
@@ -38934,7 +38934,7 @@
       <c r="E18" s="1136" t="n"/>
       <c r="F18" s="1145" t="inlineStr">
         <is>
-          <t>TB_M_MENU_VISIBILITY (proposed); per role or global is TBD.</t>
+          <t>(proposed); per role or global is TBD.</t>
         </is>
       </c>
       <c r="G18" s="1136" t="n"/>
